--- a/AAII_Financials/Yearly/ELD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ELD_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,159 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1199400</v>
+        <v>1364700</v>
       </c>
       <c r="E8" s="3">
-        <v>1294200</v>
+        <v>1180000</v>
       </c>
       <c r="F8" s="3">
-        <v>1412200</v>
+        <v>1273200</v>
       </c>
       <c r="G8" s="3">
-        <v>849800</v>
+        <v>1389300</v>
       </c>
       <c r="H8" s="3">
-        <v>631400</v>
+        <v>836000</v>
       </c>
       <c r="I8" s="3">
-        <v>538400</v>
+        <v>621100</v>
       </c>
       <c r="J8" s="3">
+        <v>529700</v>
+      </c>
+      <c r="K8" s="3">
         <v>595200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>638000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1360300</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>962500</v>
+        <v>1001400</v>
       </c>
       <c r="E9" s="3">
-        <v>895000</v>
+        <v>946900</v>
       </c>
       <c r="F9" s="3">
-        <v>912300</v>
+        <v>880500</v>
       </c>
       <c r="G9" s="3">
-        <v>671200</v>
+        <v>897500</v>
       </c>
       <c r="H9" s="3">
-        <v>516100</v>
+        <v>660300</v>
       </c>
       <c r="I9" s="3">
-        <v>364900</v>
+        <v>507700</v>
       </c>
       <c r="J9" s="3">
+        <v>359000</v>
+      </c>
+      <c r="K9" s="3">
         <v>370800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>470700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>890400</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>236900</v>
+        <v>363300</v>
       </c>
       <c r="E10" s="3">
-        <v>399200</v>
+        <v>233000</v>
       </c>
       <c r="F10" s="3">
-        <v>499900</v>
+        <v>392700</v>
       </c>
       <c r="G10" s="3">
-        <v>178600</v>
+        <v>491800</v>
       </c>
       <c r="H10" s="3">
-        <v>115300</v>
+        <v>175700</v>
       </c>
       <c r="I10" s="3">
-        <v>173400</v>
+        <v>113500</v>
       </c>
       <c r="J10" s="3">
+        <v>170600</v>
+      </c>
+      <c r="K10" s="3">
         <v>224400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>167300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>469900</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,41 +834,45 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>27000</v>
+        <v>30300</v>
       </c>
       <c r="E12" s="3">
-        <v>25200</v>
+        <v>26600</v>
       </c>
       <c r="F12" s="3">
-        <v>17200</v>
+        <v>24800</v>
       </c>
       <c r="G12" s="3">
-        <v>20100</v>
+        <v>16900</v>
       </c>
       <c r="H12" s="3">
-        <v>46500</v>
+        <v>19800</v>
       </c>
       <c r="I12" s="3">
-        <v>52600</v>
+        <v>45800</v>
       </c>
       <c r="J12" s="3">
+        <v>51800</v>
+      </c>
+      <c r="K12" s="3">
         <v>25800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>21700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>20700</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -887,42 +903,48 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>44700</v>
+        <v>13200</v>
       </c>
       <c r="E14" s="3">
-        <v>31700</v>
+        <v>44000</v>
       </c>
       <c r="F14" s="3">
-        <v>49800</v>
+        <v>31200</v>
       </c>
       <c r="G14" s="3">
-        <v>-119700</v>
+        <v>49000</v>
       </c>
       <c r="H14" s="3">
-        <v>618100</v>
+        <v>-117800</v>
       </c>
       <c r="I14" s="3">
-        <v>70100</v>
+        <v>608000</v>
       </c>
       <c r="J14" s="3">
+        <v>69000</v>
+      </c>
+      <c r="K14" s="3">
         <v>6200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2467900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3800</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -953,9 +975,12 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -966,74 +991,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1142100</v>
+        <v>1118400</v>
       </c>
       <c r="E17" s="3">
-        <v>1001300</v>
+        <v>1123600</v>
       </c>
       <c r="F17" s="3">
-        <v>1053900</v>
+        <v>985100</v>
       </c>
       <c r="G17" s="3">
-        <v>652700</v>
+        <v>1036800</v>
       </c>
       <c r="H17" s="3">
-        <v>1287200</v>
+        <v>642200</v>
       </c>
       <c r="I17" s="3">
-        <v>591400</v>
+        <v>1266300</v>
       </c>
       <c r="J17" s="3">
+        <v>581800</v>
+      </c>
+      <c r="K17" s="3">
         <v>503000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3077800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1036800</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>57300</v>
+        <v>246300</v>
       </c>
       <c r="E18" s="3">
-        <v>292900</v>
+        <v>56400</v>
       </c>
       <c r="F18" s="3">
-        <v>358300</v>
+        <v>288100</v>
       </c>
       <c r="G18" s="3">
-        <v>197100</v>
+        <v>352500</v>
       </c>
       <c r="H18" s="3">
-        <v>-655800</v>
+        <v>193900</v>
       </c>
       <c r="I18" s="3">
-        <v>-53000</v>
+        <v>-645200</v>
       </c>
       <c r="J18" s="3">
+        <v>-52200</v>
+      </c>
+      <c r="K18" s="3">
         <v>92200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2439700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>323400</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1047,173 +1079,189 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>4400</v>
+        <v>2700</v>
       </c>
       <c r="E20" s="3">
-        <v>-63800</v>
+        <v>4300</v>
       </c>
       <c r="F20" s="3">
-        <v>-63100</v>
+        <v>-62800</v>
       </c>
       <c r="G20" s="3">
-        <v>18700</v>
+        <v>-62100</v>
       </c>
       <c r="H20" s="3">
-        <v>14600</v>
+        <v>18400</v>
       </c>
       <c r="I20" s="3">
-        <v>54100</v>
+        <v>14400</v>
       </c>
       <c r="J20" s="3">
+        <v>53200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-17700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3900</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>393300</v>
+        <v>605100</v>
       </c>
       <c r="E21" s="3">
-        <v>506500</v>
+        <v>387200</v>
       </c>
       <c r="F21" s="3">
-        <v>596500</v>
+        <v>498600</v>
       </c>
       <c r="G21" s="3">
-        <v>428200</v>
+        <v>587100</v>
       </c>
       <c r="H21" s="3">
-        <v>-496500</v>
+        <v>421500</v>
       </c>
       <c r="I21" s="3">
-        <v>99700</v>
+        <v>-488400</v>
       </c>
       <c r="J21" s="3">
+        <v>98200</v>
+      </c>
+      <c r="K21" s="3">
         <v>176900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2322500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>546100</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>45400</v>
+        <v>28000</v>
       </c>
       <c r="E22" s="3">
-        <v>21300</v>
+        <v>44700</v>
       </c>
       <c r="F22" s="3">
-        <v>11400</v>
+        <v>20900</v>
       </c>
       <c r="G22" s="3">
-        <v>59700</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>17</v>
+        <v>11300</v>
+      </c>
+      <c r="H22" s="3">
+        <v>58700</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K22" s="3">
         <v>7500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>29300</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>16300</v>
+        <v>221100</v>
       </c>
       <c r="E23" s="3">
-        <v>207800</v>
+        <v>16000</v>
       </c>
       <c r="F23" s="3">
-        <v>283800</v>
+        <v>204400</v>
       </c>
       <c r="G23" s="3">
-        <v>156100</v>
+        <v>279200</v>
       </c>
       <c r="H23" s="3">
-        <v>-641200</v>
+        <v>153500</v>
       </c>
       <c r="I23" s="3">
+        <v>-630800</v>
+      </c>
+      <c r="J23" s="3">
         <v>1100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>67000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2456000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>290200</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>84200</v>
+        <v>77900</v>
       </c>
       <c r="E24" s="3">
-        <v>192500</v>
+        <v>82800</v>
       </c>
       <c r="F24" s="3">
-        <v>113300</v>
+        <v>189400</v>
       </c>
       <c r="G24" s="3">
-        <v>54700</v>
+        <v>111500</v>
       </c>
       <c r="H24" s="3">
-        <v>-119000</v>
+        <v>53800</v>
       </c>
       <c r="I24" s="3">
-        <v>26700</v>
+        <v>-117000</v>
       </c>
       <c r="J24" s="3">
+        <v>26200</v>
+      </c>
+      <c r="K24" s="3">
         <v>77300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-294800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>154500</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1244,75 +1292,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-67900</v>
+        <v>143200</v>
       </c>
       <c r="E26" s="3">
-        <v>15300</v>
+        <v>-66800</v>
       </c>
       <c r="F26" s="3">
-        <v>170500</v>
+        <v>15000</v>
       </c>
       <c r="G26" s="3">
-        <v>101400</v>
+        <v>167800</v>
       </c>
       <c r="H26" s="3">
-        <v>-522200</v>
+        <v>99700</v>
       </c>
       <c r="I26" s="3">
-        <v>-25600</v>
+        <v>-513700</v>
       </c>
       <c r="J26" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="K26" s="3">
         <v>-10300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2161200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>135700</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-67600</v>
+        <v>143700</v>
       </c>
       <c r="E27" s="3">
-        <v>14800</v>
+        <v>-66500</v>
       </c>
       <c r="F27" s="3">
-        <v>180400</v>
+        <v>14600</v>
       </c>
       <c r="G27" s="3">
-        <v>110800</v>
+        <v>177500</v>
       </c>
       <c r="H27" s="3">
-        <v>-497800</v>
+        <v>109000</v>
       </c>
       <c r="I27" s="3">
-        <v>-9800</v>
+        <v>-489700</v>
       </c>
       <c r="J27" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="K27" s="3">
         <v>-6600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2022300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>130700</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1343,42 +1400,48 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-419000</v>
+        <v>-2100</v>
       </c>
       <c r="E29" s="3">
-        <v>-201900</v>
+        <v>-412200</v>
       </c>
       <c r="F29" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="G29" s="3" t="s">
+        <v>-198700</v>
+      </c>
+      <c r="G29" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-3800</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-466800</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-29800</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="M29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1409,9 +1472,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1442,75 +1508,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-4400</v>
+        <v>-2700</v>
       </c>
       <c r="E32" s="3">
-        <v>63800</v>
+        <v>-4300</v>
       </c>
       <c r="F32" s="3">
-        <v>63100</v>
+        <v>62800</v>
       </c>
       <c r="G32" s="3">
-        <v>-18700</v>
+        <v>62100</v>
       </c>
       <c r="H32" s="3">
-        <v>-14600</v>
+        <v>-18400</v>
       </c>
       <c r="I32" s="3">
-        <v>-54100</v>
+        <v>-14400</v>
       </c>
       <c r="J32" s="3">
+        <v>-53200</v>
+      </c>
+      <c r="K32" s="3">
         <v>17700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3900</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-486700</v>
+        <v>141600</v>
       </c>
       <c r="E33" s="3">
-        <v>-187100</v>
+        <v>-478800</v>
       </c>
       <c r="F33" s="3">
-        <v>171700</v>
+        <v>-184100</v>
       </c>
       <c r="G33" s="3">
-        <v>110800</v>
+        <v>168900</v>
       </c>
       <c r="H33" s="3">
-        <v>-497800</v>
+        <v>109000</v>
       </c>
       <c r="I33" s="3">
-        <v>-13700</v>
+        <v>-489700</v>
       </c>
       <c r="J33" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-473400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2052200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>130700</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1541,80 +1616,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-486700</v>
+        <v>141600</v>
       </c>
       <c r="E35" s="3">
-        <v>-187100</v>
+        <v>-478800</v>
       </c>
       <c r="F35" s="3">
-        <v>171700</v>
+        <v>-184100</v>
       </c>
       <c r="G35" s="3">
-        <v>110800</v>
+        <v>168900</v>
       </c>
       <c r="H35" s="3">
-        <v>-497800</v>
+        <v>109000</v>
       </c>
       <c r="I35" s="3">
-        <v>-13700</v>
+        <v>-489700</v>
       </c>
       <c r="J35" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-473400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2052200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>130700</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1628,8 +1712,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1643,305 +1728,333 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>384800</v>
+        <v>731400</v>
       </c>
       <c r="E41" s="3">
-        <v>662100</v>
+        <v>378500</v>
       </c>
       <c r="F41" s="3">
-        <v>1243300</v>
+        <v>651300</v>
       </c>
       <c r="G41" s="3">
-        <v>244500</v>
+        <v>1223200</v>
       </c>
       <c r="H41" s="3">
-        <v>393800</v>
+        <v>240500</v>
       </c>
       <c r="I41" s="3">
-        <v>659600</v>
+        <v>387400</v>
       </c>
       <c r="J41" s="3">
+        <v>648900</v>
+      </c>
+      <c r="K41" s="3">
         <v>1214800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>383800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>565800</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>48300</v>
+        <v>5400</v>
       </c>
       <c r="E42" s="3">
+        <v>47500</v>
+      </c>
+      <c r="F42" s="3">
         <v>200</v>
       </c>
-      <c r="F42" s="3">
-        <v>81500</v>
-      </c>
       <c r="G42" s="3">
-        <v>9800</v>
+        <v>80100</v>
       </c>
       <c r="H42" s="3">
-        <v>12700</v>
+        <v>9600</v>
       </c>
       <c r="I42" s="3">
-        <v>14500</v>
+        <v>12500</v>
       </c>
       <c r="J42" s="3">
+        <v>14200</v>
+      </c>
+      <c r="K42" s="3">
         <v>46200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>30200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>78200</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>92200</v>
+        <v>135300</v>
       </c>
       <c r="E43" s="3">
-        <v>69800</v>
+        <v>90700</v>
       </c>
       <c r="F43" s="3">
-        <v>78100</v>
+        <v>68700</v>
       </c>
       <c r="G43" s="3">
-        <v>87300</v>
+        <v>76800</v>
       </c>
       <c r="H43" s="3">
-        <v>89700</v>
+        <v>85900</v>
       </c>
       <c r="I43" s="3">
-        <v>82000</v>
+        <v>88300</v>
       </c>
       <c r="J43" s="3">
+        <v>80600</v>
+      </c>
+      <c r="K43" s="3">
         <v>57000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>64200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>100300</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>273500</v>
+        <v>319200</v>
       </c>
       <c r="E44" s="3">
-        <v>245100</v>
+        <v>269100</v>
       </c>
       <c r="F44" s="3">
-        <v>225800</v>
+        <v>241100</v>
       </c>
       <c r="G44" s="3">
-        <v>224500</v>
+        <v>222100</v>
       </c>
       <c r="H44" s="3">
-        <v>189700</v>
+        <v>220900</v>
       </c>
       <c r="I44" s="3">
-        <v>232200</v>
+        <v>186600</v>
       </c>
       <c r="J44" s="3">
+        <v>228500</v>
+      </c>
+      <c r="K44" s="3">
         <v>166200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>233900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>284600</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>71100</v>
+        <v>67800</v>
       </c>
       <c r="E45" s="3">
-        <v>24500</v>
+        <v>69900</v>
       </c>
       <c r="F45" s="3">
-        <v>30300</v>
+        <v>24100</v>
       </c>
       <c r="G45" s="3">
-        <v>33400</v>
+        <v>29800</v>
       </c>
       <c r="H45" s="3">
-        <v>22100</v>
+        <v>32900</v>
       </c>
       <c r="I45" s="3">
-        <v>26200</v>
+        <v>21700</v>
       </c>
       <c r="J45" s="3">
+        <v>25800</v>
+      </c>
+      <c r="K45" s="3">
         <v>18100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>49900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>50400</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>869900</v>
+        <v>1259000</v>
       </c>
       <c r="E46" s="3">
-        <v>1001700</v>
+        <v>855800</v>
       </c>
       <c r="F46" s="3">
-        <v>1037300</v>
+        <v>985400</v>
       </c>
       <c r="G46" s="3">
-        <v>599500</v>
+        <v>1020400</v>
       </c>
       <c r="H46" s="3">
-        <v>708000</v>
+        <v>589800</v>
       </c>
       <c r="I46" s="3">
-        <v>1014500</v>
+        <v>696500</v>
       </c>
       <c r="J46" s="3">
+        <v>998000</v>
+      </c>
+      <c r="K46" s="3">
         <v>1502300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>762100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1079200</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>160900</v>
+        <v>244200</v>
       </c>
       <c r="E47" s="3">
-        <v>135700</v>
+        <v>158300</v>
       </c>
       <c r="F47" s="3">
-        <v>44200</v>
+        <v>133500</v>
       </c>
       <c r="G47" s="3">
-        <v>18900</v>
+        <v>43500</v>
       </c>
       <c r="H47" s="3">
-        <v>9200</v>
+        <v>18600</v>
       </c>
       <c r="I47" s="3">
-        <v>7400</v>
+        <v>9000</v>
       </c>
       <c r="J47" s="3">
+        <v>7300</v>
+      </c>
+      <c r="K47" s="3">
         <v>63900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>88800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>31400</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>4946700</v>
+        <v>5082000</v>
       </c>
       <c r="E48" s="3">
-        <v>5506400</v>
+        <v>4866500</v>
       </c>
       <c r="F48" s="3">
-        <v>5560000</v>
+        <v>5417100</v>
       </c>
       <c r="G48" s="3">
-        <v>5623300</v>
+        <v>5469900</v>
       </c>
       <c r="H48" s="3">
-        <v>5486100</v>
+        <v>5532200</v>
       </c>
       <c r="I48" s="3">
-        <v>5814800</v>
+        <v>5397200</v>
       </c>
       <c r="J48" s="3">
+        <v>5720500</v>
+      </c>
+      <c r="K48" s="3">
         <v>5014800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6326700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7600200</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>127400</v>
+        <v>125300</v>
       </c>
       <c r="E49" s="3">
-        <v>127400</v>
+        <v>125300</v>
       </c>
       <c r="F49" s="3">
-        <v>127400</v>
+        <v>125300</v>
       </c>
       <c r="G49" s="3">
-        <v>127400</v>
+        <v>125300</v>
       </c>
       <c r="H49" s="3">
-        <v>127400</v>
+        <v>125300</v>
       </c>
       <c r="I49" s="3">
-        <v>127400</v>
+        <v>125300</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>125300</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>67000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>670400</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1972,9 +2085,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2005,42 +2121,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>27000</v>
+        <v>38700</v>
       </c>
       <c r="E52" s="3">
-        <v>11000</v>
+        <v>26500</v>
       </c>
       <c r="F52" s="3">
-        <v>67500</v>
+        <v>10900</v>
       </c>
       <c r="G52" s="3">
-        <v>25500</v>
+        <v>66400</v>
       </c>
       <c r="H52" s="3">
-        <v>36400</v>
+        <v>25100</v>
       </c>
       <c r="I52" s="3">
-        <v>37700</v>
+        <v>35900</v>
       </c>
       <c r="J52" s="3">
+        <v>37100</v>
+      </c>
+      <c r="K52" s="3">
         <v>18500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>32800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>36900</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2071,42 +2193,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6131900</v>
+        <v>6749300</v>
       </c>
       <c r="E54" s="3">
-        <v>6782200</v>
+        <v>6032500</v>
       </c>
       <c r="F54" s="3">
-        <v>6782000</v>
+        <v>6672300</v>
       </c>
       <c r="G54" s="3">
-        <v>6394600</v>
+        <v>6672000</v>
       </c>
       <c r="H54" s="3">
-        <v>6367100</v>
+        <v>6290900</v>
       </c>
       <c r="I54" s="3">
-        <v>7001700</v>
+        <v>6263900</v>
       </c>
       <c r="J54" s="3">
+        <v>6888200</v>
+      </c>
+      <c r="K54" s="3">
         <v>6599500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7277400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9418000</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2120,8 +2248,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2135,58 +2264,62 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>103000</v>
+        <v>126300</v>
       </c>
       <c r="E57" s="3">
-        <v>97700</v>
+        <v>101400</v>
       </c>
       <c r="F57" s="3">
-        <v>336200</v>
+        <v>96100</v>
       </c>
       <c r="G57" s="3">
-        <v>92300</v>
+        <v>330800</v>
       </c>
       <c r="H57" s="3">
-        <v>53600</v>
+        <v>90800</v>
       </c>
       <c r="I57" s="3">
-        <v>82600</v>
+        <v>52700</v>
       </c>
       <c r="J57" s="3">
+        <v>81300</v>
+      </c>
+      <c r="K57" s="3">
         <v>60100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>129600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>106400</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6600</v>
+        <v>6800</v>
       </c>
       <c r="E58" s="3">
-        <v>9900</v>
+        <v>6500</v>
       </c>
       <c r="F58" s="3">
-        <v>107200</v>
+        <v>9800</v>
       </c>
       <c r="G58" s="3">
-        <v>105300</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>17</v>
+        <v>105500</v>
+      </c>
+      <c r="H58" s="3">
+        <v>103600</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>17</v>
@@ -2197,144 +2330,159 @@
       <c r="K58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L58" s="3">
+      <c r="L58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M58" s="3">
         <v>20800</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>180500</v>
+        <v>238000</v>
       </c>
       <c r="E59" s="3">
-        <v>176600</v>
+        <v>177600</v>
       </c>
       <c r="F59" s="3">
-        <v>163700</v>
+        <v>173800</v>
       </c>
       <c r="G59" s="3">
-        <v>107300</v>
+        <v>161000</v>
       </c>
       <c r="H59" s="3">
-        <v>141300</v>
+        <v>105600</v>
       </c>
       <c r="I59" s="3">
-        <v>74400</v>
+        <v>139000</v>
       </c>
       <c r="J59" s="3">
+        <v>73200</v>
+      </c>
+      <c r="K59" s="3">
         <v>64600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>185800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>128800</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>290100</v>
+        <v>371100</v>
       </c>
       <c r="E60" s="3">
-        <v>284200</v>
+        <v>285400</v>
       </c>
       <c r="F60" s="3">
-        <v>360400</v>
+        <v>279600</v>
       </c>
       <c r="G60" s="3">
-        <v>305000</v>
+        <v>354600</v>
       </c>
       <c r="H60" s="3">
-        <v>194900</v>
+        <v>300000</v>
       </c>
       <c r="I60" s="3">
-        <v>157000</v>
+        <v>191800</v>
       </c>
       <c r="J60" s="3">
+        <v>154500</v>
+      </c>
+      <c r="K60" s="3">
         <v>124800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>315400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>256100</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>696800</v>
+        <v>877100</v>
       </c>
       <c r="E61" s="3">
-        <v>694200</v>
+        <v>685500</v>
       </c>
       <c r="F61" s="3">
-        <v>617800</v>
+        <v>682900</v>
       </c>
       <c r="G61" s="3">
-        <v>589000</v>
+        <v>607800</v>
       </c>
       <c r="H61" s="3">
-        <v>828800</v>
+        <v>579500</v>
       </c>
       <c r="I61" s="3">
-        <v>816700</v>
+        <v>815300</v>
       </c>
       <c r="J61" s="3">
+        <v>803500</v>
+      </c>
+      <c r="K61" s="3">
         <v>813700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>785000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>748000</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>742100</v>
+        <v>748700</v>
       </c>
       <c r="E62" s="3">
-        <v>797100</v>
+        <v>730100</v>
       </c>
       <c r="F62" s="3">
-        <v>732200</v>
+        <v>784200</v>
       </c>
       <c r="G62" s="3">
-        <v>722400</v>
+        <v>720400</v>
       </c>
       <c r="H62" s="3">
-        <v>739500</v>
+        <v>710700</v>
       </c>
       <c r="I62" s="3">
-        <v>906300</v>
+        <v>727500</v>
       </c>
       <c r="J62" s="3">
+        <v>891700</v>
+      </c>
+      <c r="K62" s="3">
         <v>748500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>954500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1308800</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2365,9 +2513,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2398,9 +2549,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2431,42 +2585,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1724700</v>
+        <v>1988500</v>
       </c>
       <c r="E66" s="3">
-        <v>1871200</v>
+        <v>1696700</v>
       </c>
       <c r="F66" s="3">
-        <v>1766700</v>
+        <v>1840900</v>
       </c>
       <c r="G66" s="3">
-        <v>1697900</v>
+        <v>1738000</v>
       </c>
       <c r="H66" s="3">
-        <v>1850400</v>
+        <v>1670400</v>
       </c>
       <c r="I66" s="3">
-        <v>1990100</v>
+        <v>1820400</v>
       </c>
       <c r="J66" s="3">
+        <v>1957800</v>
+      </c>
+      <c r="K66" s="3">
         <v>1809100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2280900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2673800</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2480,8 +2640,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2512,9 +2673,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2545,9 +2709,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2578,9 +2745,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2611,42 +2781,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-3566700</v>
+        <v>-3367300</v>
       </c>
       <c r="E72" s="3">
-        <v>-3080100</v>
+        <v>-3508900</v>
       </c>
       <c r="F72" s="3">
-        <v>-2893000</v>
+        <v>-3030100</v>
       </c>
       <c r="G72" s="3">
-        <v>-3067200</v>
+        <v>-2846100</v>
       </c>
       <c r="H72" s="3">
-        <v>-3178000</v>
+        <v>-3017500</v>
       </c>
       <c r="I72" s="3">
-        <v>-2680300</v>
+        <v>-3126500</v>
       </c>
       <c r="J72" s="3">
+        <v>-2636800</v>
+      </c>
+      <c r="K72" s="3">
         <v>-2652000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2109400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-40400</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2677,9 +2853,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2710,9 +2889,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2743,42 +2925,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4407200</v>
+        <v>4760800</v>
       </c>
       <c r="E76" s="3">
-        <v>4911000</v>
+        <v>4335700</v>
       </c>
       <c r="F76" s="3">
-        <v>5015300</v>
+        <v>4831400</v>
       </c>
       <c r="G76" s="3">
-        <v>4696700</v>
+        <v>4934000</v>
       </c>
       <c r="H76" s="3">
-        <v>4516700</v>
+        <v>4620500</v>
       </c>
       <c r="I76" s="3">
-        <v>5011700</v>
+        <v>4443500</v>
       </c>
       <c r="J76" s="3">
+        <v>4930400</v>
+      </c>
+      <c r="K76" s="3">
         <v>4790400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4996500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6744200</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2809,80 +2997,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-486700</v>
+        <v>141600</v>
       </c>
       <c r="E81" s="3">
-        <v>-187100</v>
+        <v>-478800</v>
       </c>
       <c r="F81" s="3">
-        <v>171700</v>
+        <v>-184100</v>
       </c>
       <c r="G81" s="3">
-        <v>110800</v>
+        <v>168900</v>
       </c>
       <c r="H81" s="3">
-        <v>-497800</v>
+        <v>109000</v>
       </c>
       <c r="I81" s="3">
-        <v>-13700</v>
+        <v>-489700</v>
       </c>
       <c r="J81" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-473400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2052200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>130700</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2896,41 +3093,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>333400</v>
+        <v>357700</v>
       </c>
       <c r="E83" s="3">
-        <v>279000</v>
+        <v>328000</v>
       </c>
       <c r="F83" s="3">
-        <v>302900</v>
+        <v>274500</v>
       </c>
       <c r="G83" s="3">
-        <v>213700</v>
+        <v>298000</v>
       </c>
       <c r="H83" s="3">
-        <v>145400</v>
+        <v>210200</v>
       </c>
       <c r="I83" s="3">
-        <v>99200</v>
+        <v>143100</v>
       </c>
       <c r="J83" s="3">
+        <v>97600</v>
+      </c>
+      <c r="K83" s="3">
         <v>103000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>119000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>225800</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2961,9 +3162,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2994,9 +3198,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3027,9 +3234,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3060,9 +3270,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3093,42 +3306,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>289700</v>
+        <v>517700</v>
       </c>
       <c r="E89" s="3">
-        <v>498400</v>
+        <v>285000</v>
       </c>
       <c r="F89" s="3">
-        <v>646500</v>
+        <v>490400</v>
       </c>
       <c r="G89" s="3">
-        <v>228000</v>
+        <v>636000</v>
       </c>
       <c r="H89" s="3">
-        <v>92900</v>
+        <v>224300</v>
       </c>
       <c r="I89" s="3">
-        <v>38500</v>
+        <v>91400</v>
       </c>
       <c r="J89" s="3">
+        <v>37900</v>
+      </c>
+      <c r="K89" s="3">
         <v>156300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>297500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>360900</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3142,41 +3361,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-398700</v>
+        <v>-543800</v>
       </c>
       <c r="E91" s="3">
-        <v>-388000</v>
+        <v>-392200</v>
       </c>
       <c r="F91" s="3">
-        <v>-259800</v>
+        <v>-381700</v>
       </c>
       <c r="G91" s="3">
-        <v>-295100</v>
+        <v>-255600</v>
       </c>
       <c r="H91" s="3">
-        <v>-318700</v>
+        <v>-290300</v>
       </c>
       <c r="I91" s="3">
-        <v>-475800</v>
+        <v>-313500</v>
       </c>
       <c r="J91" s="3">
+        <v>-468000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-409400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-462200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-523100</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3207,9 +3430,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3240,42 +3466,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-510200</v>
+        <v>-535400</v>
       </c>
       <c r="E94" s="3">
-        <v>-365700</v>
+        <v>-501900</v>
       </c>
       <c r="F94" s="3">
-        <v>-335900</v>
+        <v>-359800</v>
       </c>
       <c r="G94" s="3">
-        <v>-259800</v>
+        <v>-330500</v>
       </c>
       <c r="H94" s="3">
-        <v>-354000</v>
+        <v>-255600</v>
       </c>
       <c r="I94" s="3">
-        <v>-572700</v>
+        <v>-348300</v>
       </c>
       <c r="J94" s="3">
+        <v>-563400</v>
+      </c>
+      <c r="K94" s="3">
         <v>662100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-523200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-489300</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3289,8 +3521,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3310,20 +3543,23 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-14600</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-14400</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-15000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-16600</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3354,9 +3590,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3387,9 +3626,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3420,42 +3662,48 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-56900</v>
+        <v>370600</v>
       </c>
       <c r="E100" s="3">
-        <v>-92300</v>
+        <v>-55900</v>
       </c>
       <c r="F100" s="3">
-        <v>66700</v>
+        <v>-90800</v>
       </c>
       <c r="G100" s="3">
-        <v>-117500</v>
+        <v>65600</v>
       </c>
       <c r="H100" s="3">
-        <v>-4600</v>
+        <v>-115600</v>
       </c>
       <c r="I100" s="3">
-        <v>-21100</v>
+        <v>-4500</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>-20700</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-54400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>12900</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3486,40 +3734,46 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-277300</v>
+        <v>351800</v>
       </c>
       <c r="E102" s="3">
-        <v>40400</v>
+        <v>-272800</v>
       </c>
       <c r="F102" s="3">
-        <v>377200</v>
+        <v>39700</v>
       </c>
       <c r="G102" s="3">
-        <v>-149300</v>
+        <v>371100</v>
       </c>
       <c r="H102" s="3">
-        <v>-265700</v>
+        <v>-146900</v>
       </c>
       <c r="I102" s="3">
-        <v>-555200</v>
+        <v>-261400</v>
       </c>
       <c r="J102" s="3">
+        <v>-546200</v>
+      </c>
+      <c r="K102" s="3">
         <v>818400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-280100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-115500</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ELD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ELD_YR_FIN.xlsx
@@ -717,25 +717,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1364700</v>
+        <v>1383900</v>
       </c>
       <c r="E8" s="3">
-        <v>1180000</v>
+        <v>1196500</v>
       </c>
       <c r="F8" s="3">
-        <v>1273200</v>
+        <v>1291100</v>
       </c>
       <c r="G8" s="3">
-        <v>1389300</v>
+        <v>1408800</v>
       </c>
       <c r="H8" s="3">
-        <v>836000</v>
+        <v>847800</v>
       </c>
       <c r="I8" s="3">
-        <v>621100</v>
+        <v>629900</v>
       </c>
       <c r="J8" s="3">
-        <v>529700</v>
+        <v>537100</v>
       </c>
       <c r="K8" s="3">
         <v>595200</v>
@@ -753,25 +753,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1001400</v>
+        <v>1015500</v>
       </c>
       <c r="E9" s="3">
-        <v>946900</v>
+        <v>960200</v>
       </c>
       <c r="F9" s="3">
-        <v>880500</v>
+        <v>892900</v>
       </c>
       <c r="G9" s="3">
-        <v>897500</v>
+        <v>910100</v>
       </c>
       <c r="H9" s="3">
-        <v>660300</v>
+        <v>669600</v>
       </c>
       <c r="I9" s="3">
-        <v>507700</v>
+        <v>514800</v>
       </c>
       <c r="J9" s="3">
-        <v>359000</v>
+        <v>364100</v>
       </c>
       <c r="K9" s="3">
         <v>370800</v>
@@ -789,25 +789,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>363300</v>
+        <v>368400</v>
       </c>
       <c r="E10" s="3">
-        <v>233000</v>
+        <v>236300</v>
       </c>
       <c r="F10" s="3">
-        <v>392700</v>
+        <v>398200</v>
       </c>
       <c r="G10" s="3">
-        <v>491800</v>
+        <v>498700</v>
       </c>
       <c r="H10" s="3">
-        <v>175700</v>
+        <v>178200</v>
       </c>
       <c r="I10" s="3">
-        <v>113500</v>
+        <v>115000</v>
       </c>
       <c r="J10" s="3">
-        <v>170600</v>
+        <v>173000</v>
       </c>
       <c r="K10" s="3">
         <v>224400</v>
@@ -841,25 +841,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>30300</v>
+        <v>30800</v>
       </c>
       <c r="E12" s="3">
-        <v>26600</v>
+        <v>26900</v>
       </c>
       <c r="F12" s="3">
-        <v>24800</v>
+        <v>25100</v>
       </c>
       <c r="G12" s="3">
-        <v>16900</v>
+        <v>17100</v>
       </c>
       <c r="H12" s="3">
-        <v>19800</v>
+        <v>20100</v>
       </c>
       <c r="I12" s="3">
-        <v>45800</v>
+        <v>46400</v>
       </c>
       <c r="J12" s="3">
-        <v>51800</v>
+        <v>52500</v>
       </c>
       <c r="K12" s="3">
         <v>25800</v>
@@ -913,25 +913,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>13200</v>
+        <v>13300</v>
       </c>
       <c r="E14" s="3">
-        <v>44000</v>
+        <v>44600</v>
       </c>
       <c r="F14" s="3">
-        <v>31200</v>
+        <v>31600</v>
       </c>
       <c r="G14" s="3">
-        <v>49000</v>
+        <v>49700</v>
       </c>
       <c r="H14" s="3">
-        <v>-117800</v>
+        <v>-119500</v>
       </c>
       <c r="I14" s="3">
-        <v>608000</v>
+        <v>616600</v>
       </c>
       <c r="J14" s="3">
-        <v>69000</v>
+        <v>69900</v>
       </c>
       <c r="K14" s="3">
         <v>6200</v>
@@ -998,25 +998,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1118400</v>
+        <v>1134100</v>
       </c>
       <c r="E17" s="3">
-        <v>1123600</v>
+        <v>1139300</v>
       </c>
       <c r="F17" s="3">
-        <v>985100</v>
+        <v>998900</v>
       </c>
       <c r="G17" s="3">
-        <v>1036800</v>
+        <v>1051300</v>
       </c>
       <c r="H17" s="3">
-        <v>642200</v>
+        <v>651200</v>
       </c>
       <c r="I17" s="3">
-        <v>1266300</v>
+        <v>1284100</v>
       </c>
       <c r="J17" s="3">
-        <v>581800</v>
+        <v>590000</v>
       </c>
       <c r="K17" s="3">
         <v>503000</v>
@@ -1034,25 +1034,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>246300</v>
+        <v>249800</v>
       </c>
       <c r="E18" s="3">
-        <v>56400</v>
+        <v>57200</v>
       </c>
       <c r="F18" s="3">
-        <v>288100</v>
+        <v>292200</v>
       </c>
       <c r="G18" s="3">
-        <v>352500</v>
+        <v>357500</v>
       </c>
       <c r="H18" s="3">
-        <v>193900</v>
+        <v>196600</v>
       </c>
       <c r="I18" s="3">
-        <v>-645200</v>
+        <v>-654200</v>
       </c>
       <c r="J18" s="3">
-        <v>-52200</v>
+        <v>-52900</v>
       </c>
       <c r="K18" s="3">
         <v>92200</v>
@@ -1086,25 +1086,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="E20" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="F20" s="3">
-        <v>-62800</v>
+        <v>-63700</v>
       </c>
       <c r="G20" s="3">
-        <v>-62100</v>
+        <v>-63000</v>
       </c>
       <c r="H20" s="3">
-        <v>18400</v>
+        <v>18600</v>
       </c>
       <c r="I20" s="3">
-        <v>14400</v>
+        <v>14600</v>
       </c>
       <c r="J20" s="3">
-        <v>53200</v>
+        <v>54000</v>
       </c>
       <c r="K20" s="3">
         <v>-17700</v>
@@ -1122,25 +1122,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>605100</v>
+        <v>616200</v>
       </c>
       <c r="E21" s="3">
-        <v>387200</v>
+        <v>395000</v>
       </c>
       <c r="F21" s="3">
-        <v>498600</v>
+        <v>507600</v>
       </c>
       <c r="G21" s="3">
-        <v>587100</v>
+        <v>597500</v>
       </c>
       <c r="H21" s="3">
-        <v>421500</v>
+        <v>428900</v>
       </c>
       <c r="I21" s="3">
-        <v>-488400</v>
+        <v>-494200</v>
       </c>
       <c r="J21" s="3">
-        <v>98200</v>
+        <v>100300</v>
       </c>
       <c r="K21" s="3">
         <v>176900</v>
@@ -1158,19 +1158,19 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>28000</v>
+        <v>28400</v>
       </c>
       <c r="E22" s="3">
-        <v>44700</v>
+        <v>45300</v>
       </c>
       <c r="F22" s="3">
-        <v>20900</v>
+        <v>21200</v>
       </c>
       <c r="G22" s="3">
-        <v>11300</v>
+        <v>11400</v>
       </c>
       <c r="H22" s="3">
-        <v>58700</v>
+        <v>59600</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>17</v>
@@ -1194,22 +1194,22 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>221100</v>
+        <v>224200</v>
       </c>
       <c r="E23" s="3">
-        <v>16000</v>
+        <v>16300</v>
       </c>
       <c r="F23" s="3">
-        <v>204400</v>
+        <v>207300</v>
       </c>
       <c r="G23" s="3">
-        <v>279200</v>
+        <v>283100</v>
       </c>
       <c r="H23" s="3">
-        <v>153500</v>
+        <v>155700</v>
       </c>
       <c r="I23" s="3">
-        <v>-630800</v>
+        <v>-639600</v>
       </c>
       <c r="J23" s="3">
         <v>1100</v>
@@ -1230,25 +1230,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>77900</v>
+        <v>79000</v>
       </c>
       <c r="E24" s="3">
-        <v>82800</v>
+        <v>84000</v>
       </c>
       <c r="F24" s="3">
-        <v>189400</v>
+        <v>192100</v>
       </c>
       <c r="G24" s="3">
-        <v>111500</v>
+        <v>113000</v>
       </c>
       <c r="H24" s="3">
-        <v>53800</v>
+        <v>54600</v>
       </c>
       <c r="I24" s="3">
-        <v>-117000</v>
+        <v>-118700</v>
       </c>
       <c r="J24" s="3">
-        <v>26200</v>
+        <v>26600</v>
       </c>
       <c r="K24" s="3">
         <v>77300</v>
@@ -1302,25 +1302,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>143200</v>
+        <v>145200</v>
       </c>
       <c r="E26" s="3">
-        <v>-66800</v>
+        <v>-67700</v>
       </c>
       <c r="F26" s="3">
-        <v>15000</v>
+        <v>15200</v>
       </c>
       <c r="G26" s="3">
-        <v>167800</v>
+        <v>170100</v>
       </c>
       <c r="H26" s="3">
-        <v>99700</v>
+        <v>101100</v>
       </c>
       <c r="I26" s="3">
-        <v>-513700</v>
+        <v>-520900</v>
       </c>
       <c r="J26" s="3">
-        <v>-25200</v>
+        <v>-25500</v>
       </c>
       <c r="K26" s="3">
         <v>-10300</v>
@@ -1338,25 +1338,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>143700</v>
+        <v>145700</v>
       </c>
       <c r="E27" s="3">
-        <v>-66500</v>
+        <v>-67500</v>
       </c>
       <c r="F27" s="3">
-        <v>14600</v>
+        <v>14800</v>
       </c>
       <c r="G27" s="3">
-        <v>177500</v>
+        <v>180000</v>
       </c>
       <c r="H27" s="3">
-        <v>109000</v>
+        <v>110600</v>
       </c>
       <c r="I27" s="3">
-        <v>-489700</v>
+        <v>-496600</v>
       </c>
       <c r="J27" s="3">
-        <v>-9700</v>
+        <v>-9800</v>
       </c>
       <c r="K27" s="3">
         <v>-6600</v>
@@ -1413,13 +1413,13 @@
         <v>-2100</v>
       </c>
       <c r="E29" s="3">
-        <v>-412200</v>
+        <v>-418000</v>
       </c>
       <c r="F29" s="3">
-        <v>-198700</v>
+        <v>-201400</v>
       </c>
       <c r="G29" s="3">
-        <v>-8600</v>
+        <v>-8700</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>17</v>
@@ -1518,25 +1518,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2700</v>
+        <v>-2800</v>
       </c>
       <c r="E32" s="3">
-        <v>-4300</v>
+        <v>-4400</v>
       </c>
       <c r="F32" s="3">
-        <v>62800</v>
+        <v>63700</v>
       </c>
       <c r="G32" s="3">
-        <v>62100</v>
+        <v>63000</v>
       </c>
       <c r="H32" s="3">
-        <v>-18400</v>
+        <v>-18600</v>
       </c>
       <c r="I32" s="3">
-        <v>-14400</v>
+        <v>-14600</v>
       </c>
       <c r="J32" s="3">
-        <v>-53200</v>
+        <v>-54000</v>
       </c>
       <c r="K32" s="3">
         <v>17700</v>
@@ -1554,25 +1554,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>141600</v>
+        <v>143600</v>
       </c>
       <c r="E33" s="3">
-        <v>-478800</v>
+        <v>-485500</v>
       </c>
       <c r="F33" s="3">
-        <v>-184100</v>
+        <v>-186600</v>
       </c>
       <c r="G33" s="3">
-        <v>168900</v>
+        <v>171200</v>
       </c>
       <c r="H33" s="3">
-        <v>109000</v>
+        <v>110600</v>
       </c>
       <c r="I33" s="3">
-        <v>-489700</v>
+        <v>-496600</v>
       </c>
       <c r="J33" s="3">
-        <v>-13400</v>
+        <v>-13600</v>
       </c>
       <c r="K33" s="3">
         <v>-473400</v>
@@ -1626,25 +1626,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>141600</v>
+        <v>143600</v>
       </c>
       <c r="E35" s="3">
-        <v>-478800</v>
+        <v>-485500</v>
       </c>
       <c r="F35" s="3">
-        <v>-184100</v>
+        <v>-186600</v>
       </c>
       <c r="G35" s="3">
-        <v>168900</v>
+        <v>171200</v>
       </c>
       <c r="H35" s="3">
-        <v>109000</v>
+        <v>110600</v>
       </c>
       <c r="I35" s="3">
-        <v>-489700</v>
+        <v>-496600</v>
       </c>
       <c r="J35" s="3">
-        <v>-13400</v>
+        <v>-13600</v>
       </c>
       <c r="K35" s="3">
         <v>-473400</v>
@@ -1735,25 +1735,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>731400</v>
+        <v>741600</v>
       </c>
       <c r="E41" s="3">
-        <v>378500</v>
+        <v>383900</v>
       </c>
       <c r="F41" s="3">
-        <v>651300</v>
+        <v>660500</v>
       </c>
       <c r="G41" s="3">
-        <v>1223200</v>
+        <v>1240400</v>
       </c>
       <c r="H41" s="3">
-        <v>240500</v>
+        <v>243900</v>
       </c>
       <c r="I41" s="3">
-        <v>387400</v>
+        <v>392900</v>
       </c>
       <c r="J41" s="3">
-        <v>648900</v>
+        <v>658000</v>
       </c>
       <c r="K41" s="3">
         <v>1214800</v>
@@ -1774,22 +1774,22 @@
         <v>5400</v>
       </c>
       <c r="E42" s="3">
-        <v>47500</v>
+        <v>48200</v>
       </c>
       <c r="F42" s="3">
         <v>200</v>
       </c>
       <c r="G42" s="3">
-        <v>80100</v>
+        <v>81300</v>
       </c>
       <c r="H42" s="3">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="I42" s="3">
-        <v>12500</v>
+        <v>12600</v>
       </c>
       <c r="J42" s="3">
-        <v>14200</v>
+        <v>14400</v>
       </c>
       <c r="K42" s="3">
         <v>46200</v>
@@ -1807,25 +1807,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>135300</v>
+        <v>137200</v>
       </c>
       <c r="E43" s="3">
-        <v>90700</v>
+        <v>92000</v>
       </c>
       <c r="F43" s="3">
-        <v>68700</v>
+        <v>69600</v>
       </c>
       <c r="G43" s="3">
-        <v>76800</v>
+        <v>77900</v>
       </c>
       <c r="H43" s="3">
-        <v>85900</v>
+        <v>87100</v>
       </c>
       <c r="I43" s="3">
-        <v>88300</v>
+        <v>89500</v>
       </c>
       <c r="J43" s="3">
-        <v>80600</v>
+        <v>81800</v>
       </c>
       <c r="K43" s="3">
         <v>57000</v>
@@ -1843,25 +1843,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>319200</v>
+        <v>323700</v>
       </c>
       <c r="E44" s="3">
-        <v>269100</v>
+        <v>272900</v>
       </c>
       <c r="F44" s="3">
-        <v>241100</v>
+        <v>244500</v>
       </c>
       <c r="G44" s="3">
-        <v>222100</v>
+        <v>225200</v>
       </c>
       <c r="H44" s="3">
-        <v>220900</v>
+        <v>224000</v>
       </c>
       <c r="I44" s="3">
-        <v>186600</v>
+        <v>189200</v>
       </c>
       <c r="J44" s="3">
-        <v>228500</v>
+        <v>231700</v>
       </c>
       <c r="K44" s="3">
         <v>166200</v>
@@ -1879,25 +1879,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>67800</v>
+        <v>68800</v>
       </c>
       <c r="E45" s="3">
-        <v>69900</v>
+        <v>70900</v>
       </c>
       <c r="F45" s="3">
-        <v>24100</v>
+        <v>24500</v>
       </c>
       <c r="G45" s="3">
-        <v>29800</v>
+        <v>30200</v>
       </c>
       <c r="H45" s="3">
-        <v>32900</v>
+        <v>33300</v>
       </c>
       <c r="I45" s="3">
-        <v>21700</v>
+        <v>22000</v>
       </c>
       <c r="J45" s="3">
-        <v>25800</v>
+        <v>26200</v>
       </c>
       <c r="K45" s="3">
         <v>18100</v>
@@ -1915,25 +1915,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1259000</v>
+        <v>1276700</v>
       </c>
       <c r="E46" s="3">
-        <v>855800</v>
+        <v>867900</v>
       </c>
       <c r="F46" s="3">
-        <v>985400</v>
+        <v>999300</v>
       </c>
       <c r="G46" s="3">
-        <v>1020400</v>
+        <v>1034800</v>
       </c>
       <c r="H46" s="3">
-        <v>589800</v>
+        <v>598100</v>
       </c>
       <c r="I46" s="3">
-        <v>696500</v>
+        <v>706300</v>
       </c>
       <c r="J46" s="3">
-        <v>998000</v>
+        <v>1012000</v>
       </c>
       <c r="K46" s="3">
         <v>1502300</v>
@@ -1951,25 +1951,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>244200</v>
+        <v>247600</v>
       </c>
       <c r="E47" s="3">
-        <v>158300</v>
+        <v>160600</v>
       </c>
       <c r="F47" s="3">
-        <v>133500</v>
+        <v>135400</v>
       </c>
       <c r="G47" s="3">
-        <v>43500</v>
+        <v>44100</v>
       </c>
       <c r="H47" s="3">
-        <v>18600</v>
+        <v>18900</v>
       </c>
       <c r="I47" s="3">
-        <v>9000</v>
+        <v>9100</v>
       </c>
       <c r="J47" s="3">
-        <v>7300</v>
+        <v>7400</v>
       </c>
       <c r="K47" s="3">
         <v>63900</v>
@@ -1987,25 +1987,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5082000</v>
+        <v>5153400</v>
       </c>
       <c r="E48" s="3">
-        <v>4866500</v>
+        <v>4934800</v>
       </c>
       <c r="F48" s="3">
-        <v>5417100</v>
+        <v>5493200</v>
       </c>
       <c r="G48" s="3">
-        <v>5469900</v>
+        <v>5546700</v>
       </c>
       <c r="H48" s="3">
-        <v>5532200</v>
+        <v>5609800</v>
       </c>
       <c r="I48" s="3">
-        <v>5397200</v>
+        <v>5473000</v>
       </c>
       <c r="J48" s="3">
-        <v>5720500</v>
+        <v>5800800</v>
       </c>
       <c r="K48" s="3">
         <v>5014800</v>
@@ -2023,25 +2023,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>125300</v>
+        <v>127100</v>
       </c>
       <c r="E49" s="3">
-        <v>125300</v>
+        <v>127100</v>
       </c>
       <c r="F49" s="3">
-        <v>125300</v>
+        <v>127100</v>
       </c>
       <c r="G49" s="3">
-        <v>125300</v>
+        <v>127100</v>
       </c>
       <c r="H49" s="3">
-        <v>125300</v>
+        <v>127100</v>
       </c>
       <c r="I49" s="3">
-        <v>125300</v>
+        <v>127100</v>
       </c>
       <c r="J49" s="3">
-        <v>125300</v>
+        <v>127100</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -2131,25 +2131,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>38700</v>
+        <v>39300</v>
       </c>
       <c r="E52" s="3">
-        <v>26500</v>
+        <v>26900</v>
       </c>
       <c r="F52" s="3">
-        <v>10900</v>
+        <v>11000</v>
       </c>
       <c r="G52" s="3">
-        <v>66400</v>
+        <v>67300</v>
       </c>
       <c r="H52" s="3">
-        <v>25100</v>
+        <v>25400</v>
       </c>
       <c r="I52" s="3">
-        <v>35900</v>
+        <v>36400</v>
       </c>
       <c r="J52" s="3">
-        <v>37100</v>
+        <v>37600</v>
       </c>
       <c r="K52" s="3">
         <v>18500</v>
@@ -2203,25 +2203,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6749300</v>
+        <v>6844000</v>
       </c>
       <c r="E54" s="3">
-        <v>6032500</v>
+        <v>6117200</v>
       </c>
       <c r="F54" s="3">
-        <v>6672300</v>
+        <v>6766000</v>
       </c>
       <c r="G54" s="3">
-        <v>6672000</v>
+        <v>6765700</v>
       </c>
       <c r="H54" s="3">
-        <v>6290900</v>
+        <v>6379200</v>
       </c>
       <c r="I54" s="3">
-        <v>6263900</v>
+        <v>6351800</v>
       </c>
       <c r="J54" s="3">
-        <v>6888200</v>
+        <v>6984900</v>
       </c>
       <c r="K54" s="3">
         <v>6599500</v>
@@ -2271,25 +2271,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>126300</v>
+        <v>128100</v>
       </c>
       <c r="E57" s="3">
-        <v>101400</v>
+        <v>102800</v>
       </c>
       <c r="F57" s="3">
-        <v>96100</v>
+        <v>97400</v>
       </c>
       <c r="G57" s="3">
-        <v>330800</v>
+        <v>335400</v>
       </c>
       <c r="H57" s="3">
-        <v>90800</v>
+        <v>92100</v>
       </c>
       <c r="I57" s="3">
-        <v>52700</v>
+        <v>53500</v>
       </c>
       <c r="J57" s="3">
-        <v>81300</v>
+        <v>82400</v>
       </c>
       <c r="K57" s="3">
         <v>60100</v>
@@ -2307,19 +2307,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6800</v>
+        <v>6900</v>
       </c>
       <c r="E58" s="3">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="F58" s="3">
-        <v>9800</v>
+        <v>9900</v>
       </c>
       <c r="G58" s="3">
-        <v>105500</v>
+        <v>107000</v>
       </c>
       <c r="H58" s="3">
-        <v>103600</v>
+        <v>105100</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>17</v>
@@ -2343,25 +2343,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>238000</v>
+        <v>241300</v>
       </c>
       <c r="E59" s="3">
-        <v>177600</v>
+        <v>180100</v>
       </c>
       <c r="F59" s="3">
-        <v>173800</v>
+        <v>176200</v>
       </c>
       <c r="G59" s="3">
-        <v>161000</v>
+        <v>163300</v>
       </c>
       <c r="H59" s="3">
-        <v>105600</v>
+        <v>107100</v>
       </c>
       <c r="I59" s="3">
-        <v>139000</v>
+        <v>141000</v>
       </c>
       <c r="J59" s="3">
-        <v>73200</v>
+        <v>74200</v>
       </c>
       <c r="K59" s="3">
         <v>64600</v>
@@ -2379,25 +2379,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>371100</v>
+        <v>376300</v>
       </c>
       <c r="E60" s="3">
-        <v>285400</v>
+        <v>289500</v>
       </c>
       <c r="F60" s="3">
-        <v>279600</v>
+        <v>283600</v>
       </c>
       <c r="G60" s="3">
-        <v>354600</v>
+        <v>359600</v>
       </c>
       <c r="H60" s="3">
-        <v>300000</v>
+        <v>304200</v>
       </c>
       <c r="I60" s="3">
-        <v>191800</v>
+        <v>194400</v>
       </c>
       <c r="J60" s="3">
-        <v>154500</v>
+        <v>156600</v>
       </c>
       <c r="K60" s="3">
         <v>124800</v>
@@ -2415,25 +2415,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>877100</v>
+        <v>889400</v>
       </c>
       <c r="E61" s="3">
-        <v>685500</v>
+        <v>695100</v>
       </c>
       <c r="F61" s="3">
-        <v>682900</v>
+        <v>692500</v>
       </c>
       <c r="G61" s="3">
-        <v>607800</v>
+        <v>616300</v>
       </c>
       <c r="H61" s="3">
-        <v>579500</v>
+        <v>587600</v>
       </c>
       <c r="I61" s="3">
-        <v>815300</v>
+        <v>826800</v>
       </c>
       <c r="J61" s="3">
-        <v>803500</v>
+        <v>814800</v>
       </c>
       <c r="K61" s="3">
         <v>813700</v>
@@ -2451,25 +2451,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>748700</v>
+        <v>759200</v>
       </c>
       <c r="E62" s="3">
-        <v>730100</v>
+        <v>740300</v>
       </c>
       <c r="F62" s="3">
-        <v>784200</v>
+        <v>795200</v>
       </c>
       <c r="G62" s="3">
-        <v>720400</v>
+        <v>730500</v>
       </c>
       <c r="H62" s="3">
-        <v>710700</v>
+        <v>720600</v>
       </c>
       <c r="I62" s="3">
-        <v>727500</v>
+        <v>737700</v>
       </c>
       <c r="J62" s="3">
-        <v>891700</v>
+        <v>904200</v>
       </c>
       <c r="K62" s="3">
         <v>748500</v>
@@ -2595,25 +2595,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1988500</v>
+        <v>2016400</v>
       </c>
       <c r="E66" s="3">
-        <v>1696700</v>
+        <v>1720500</v>
       </c>
       <c r="F66" s="3">
-        <v>1840900</v>
+        <v>1866700</v>
       </c>
       <c r="G66" s="3">
-        <v>1738000</v>
+        <v>1762400</v>
       </c>
       <c r="H66" s="3">
-        <v>1670400</v>
+        <v>1693900</v>
       </c>
       <c r="I66" s="3">
-        <v>1820400</v>
+        <v>1846000</v>
       </c>
       <c r="J66" s="3">
-        <v>1957800</v>
+        <v>1985300</v>
       </c>
       <c r="K66" s="3">
         <v>1809100</v>
@@ -2791,25 +2791,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-3367300</v>
+        <v>-3414600</v>
       </c>
       <c r="E72" s="3">
-        <v>-3508900</v>
+        <v>-3558200</v>
       </c>
       <c r="F72" s="3">
-        <v>-3030100</v>
+        <v>-3072700</v>
       </c>
       <c r="G72" s="3">
-        <v>-2846100</v>
+        <v>-2886000</v>
       </c>
       <c r="H72" s="3">
-        <v>-3017500</v>
+        <v>-3059800</v>
       </c>
       <c r="I72" s="3">
-        <v>-3126500</v>
+        <v>-3170400</v>
       </c>
       <c r="J72" s="3">
-        <v>-2636800</v>
+        <v>-2673800</v>
       </c>
       <c r="K72" s="3">
         <v>-2652000</v>
@@ -2935,25 +2935,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4760800</v>
+        <v>4827600</v>
       </c>
       <c r="E76" s="3">
-        <v>4335700</v>
+        <v>4396600</v>
       </c>
       <c r="F76" s="3">
-        <v>4831400</v>
+        <v>4899300</v>
       </c>
       <c r="G76" s="3">
-        <v>4934000</v>
+        <v>5003300</v>
       </c>
       <c r="H76" s="3">
-        <v>4620500</v>
+        <v>4685400</v>
       </c>
       <c r="I76" s="3">
-        <v>4443500</v>
+        <v>4505900</v>
       </c>
       <c r="J76" s="3">
-        <v>4930400</v>
+        <v>4999700</v>
       </c>
       <c r="K76" s="3">
         <v>4790400</v>
@@ -3048,25 +3048,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>141600</v>
+        <v>143600</v>
       </c>
       <c r="E81" s="3">
-        <v>-478800</v>
+        <v>-485500</v>
       </c>
       <c r="F81" s="3">
-        <v>-184100</v>
+        <v>-186600</v>
       </c>
       <c r="G81" s="3">
-        <v>168900</v>
+        <v>171200</v>
       </c>
       <c r="H81" s="3">
-        <v>109000</v>
+        <v>110600</v>
       </c>
       <c r="I81" s="3">
-        <v>-489700</v>
+        <v>-496600</v>
       </c>
       <c r="J81" s="3">
-        <v>-13400</v>
+        <v>-13600</v>
       </c>
       <c r="K81" s="3">
         <v>-473400</v>
@@ -3100,25 +3100,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>357700</v>
+        <v>362700</v>
       </c>
       <c r="E83" s="3">
-        <v>328000</v>
+        <v>332600</v>
       </c>
       <c r="F83" s="3">
-        <v>274500</v>
+        <v>278400</v>
       </c>
       <c r="G83" s="3">
-        <v>298000</v>
+        <v>302200</v>
       </c>
       <c r="H83" s="3">
-        <v>210200</v>
+        <v>213100</v>
       </c>
       <c r="I83" s="3">
-        <v>143100</v>
+        <v>145100</v>
       </c>
       <c r="J83" s="3">
-        <v>97600</v>
+        <v>99000</v>
       </c>
       <c r="K83" s="3">
         <v>103000</v>
@@ -3316,25 +3316,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>517700</v>
+        <v>524900</v>
       </c>
       <c r="E89" s="3">
-        <v>285000</v>
+        <v>289000</v>
       </c>
       <c r="F89" s="3">
-        <v>490400</v>
+        <v>497200</v>
       </c>
       <c r="G89" s="3">
-        <v>636000</v>
+        <v>644900</v>
       </c>
       <c r="H89" s="3">
-        <v>224300</v>
+        <v>227500</v>
       </c>
       <c r="I89" s="3">
-        <v>91400</v>
+        <v>92700</v>
       </c>
       <c r="J89" s="3">
-        <v>37900</v>
+        <v>38400</v>
       </c>
       <c r="K89" s="3">
         <v>156300</v>
@@ -3368,25 +3368,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-543800</v>
+        <v>-551400</v>
       </c>
       <c r="E91" s="3">
-        <v>-392200</v>
+        <v>-397700</v>
       </c>
       <c r="F91" s="3">
-        <v>-381700</v>
+        <v>-387100</v>
       </c>
       <c r="G91" s="3">
-        <v>-255600</v>
+        <v>-259200</v>
       </c>
       <c r="H91" s="3">
-        <v>-290300</v>
+        <v>-294300</v>
       </c>
       <c r="I91" s="3">
-        <v>-313500</v>
+        <v>-317900</v>
       </c>
       <c r="J91" s="3">
-        <v>-468000</v>
+        <v>-474600</v>
       </c>
       <c r="K91" s="3">
         <v>-409400</v>
@@ -3476,25 +3476,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-535400</v>
+        <v>-543000</v>
       </c>
       <c r="E94" s="3">
-        <v>-501900</v>
+        <v>-508900</v>
       </c>
       <c r="F94" s="3">
-        <v>-359800</v>
+        <v>-364800</v>
       </c>
       <c r="G94" s="3">
-        <v>-330500</v>
+        <v>-335100</v>
       </c>
       <c r="H94" s="3">
-        <v>-255600</v>
+        <v>-259200</v>
       </c>
       <c r="I94" s="3">
-        <v>-348300</v>
+        <v>-353200</v>
       </c>
       <c r="J94" s="3">
-        <v>-563400</v>
+        <v>-571300</v>
       </c>
       <c r="K94" s="3">
         <v>662100</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>-14400</v>
+        <v>-14600</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3672,25 +3672,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>370600</v>
+        <v>375800</v>
       </c>
       <c r="E100" s="3">
-        <v>-55900</v>
+        <v>-56700</v>
       </c>
       <c r="F100" s="3">
-        <v>-90800</v>
+        <v>-92100</v>
       </c>
       <c r="G100" s="3">
-        <v>65600</v>
+        <v>66500</v>
       </c>
       <c r="H100" s="3">
-        <v>-115600</v>
+        <v>-117300</v>
       </c>
       <c r="I100" s="3">
-        <v>-4500</v>
+        <v>-4600</v>
       </c>
       <c r="J100" s="3">
-        <v>-20700</v>
+        <v>-21000</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -3744,25 +3744,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>351800</v>
+        <v>356700</v>
       </c>
       <c r="E102" s="3">
-        <v>-272800</v>
+        <v>-276600</v>
       </c>
       <c r="F102" s="3">
-        <v>39700</v>
+        <v>40300</v>
       </c>
       <c r="G102" s="3">
-        <v>371100</v>
+        <v>376300</v>
       </c>
       <c r="H102" s="3">
-        <v>-146900</v>
+        <v>-149000</v>
       </c>
       <c r="I102" s="3">
-        <v>-261400</v>
+        <v>-265100</v>
       </c>
       <c r="J102" s="3">
-        <v>-546200</v>
+        <v>-553900</v>
       </c>
       <c r="K102" s="3">
         <v>818400</v>

--- a/AAII_Financials/Yearly/ELD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ELD_YR_FIN.xlsx
@@ -717,25 +717,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1383900</v>
+        <v>1370000</v>
       </c>
       <c r="E8" s="3">
-        <v>1196500</v>
+        <v>1184600</v>
       </c>
       <c r="F8" s="3">
-        <v>1291100</v>
+        <v>1278200</v>
       </c>
       <c r="G8" s="3">
-        <v>1408800</v>
+        <v>1394800</v>
       </c>
       <c r="H8" s="3">
-        <v>847800</v>
+        <v>839300</v>
       </c>
       <c r="I8" s="3">
-        <v>629900</v>
+        <v>623600</v>
       </c>
       <c r="J8" s="3">
-        <v>537100</v>
+        <v>531700</v>
       </c>
       <c r="K8" s="3">
         <v>595200</v>
@@ -753,25 +753,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1015500</v>
+        <v>1005300</v>
       </c>
       <c r="E9" s="3">
-        <v>960200</v>
+        <v>950600</v>
       </c>
       <c r="F9" s="3">
-        <v>892900</v>
+        <v>884000</v>
       </c>
       <c r="G9" s="3">
-        <v>910100</v>
+        <v>901000</v>
       </c>
       <c r="H9" s="3">
-        <v>669600</v>
+        <v>662900</v>
       </c>
       <c r="I9" s="3">
-        <v>514800</v>
+        <v>509700</v>
       </c>
       <c r="J9" s="3">
-        <v>364100</v>
+        <v>360400</v>
       </c>
       <c r="K9" s="3">
         <v>370800</v>
@@ -789,25 +789,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>368400</v>
+        <v>364700</v>
       </c>
       <c r="E10" s="3">
-        <v>236300</v>
+        <v>234000</v>
       </c>
       <c r="F10" s="3">
-        <v>398200</v>
+        <v>394200</v>
       </c>
       <c r="G10" s="3">
-        <v>498700</v>
+        <v>493700</v>
       </c>
       <c r="H10" s="3">
-        <v>178200</v>
+        <v>176400</v>
       </c>
       <c r="I10" s="3">
-        <v>115000</v>
+        <v>113900</v>
       </c>
       <c r="J10" s="3">
-        <v>173000</v>
+        <v>171300</v>
       </c>
       <c r="K10" s="3">
         <v>224400</v>
@@ -841,25 +841,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>30800</v>
+        <v>30500</v>
       </c>
       <c r="E12" s="3">
-        <v>26900</v>
+        <v>26700</v>
       </c>
       <c r="F12" s="3">
-        <v>25100</v>
+        <v>24900</v>
       </c>
       <c r="G12" s="3">
-        <v>17100</v>
+        <v>17000</v>
       </c>
       <c r="H12" s="3">
-        <v>20100</v>
+        <v>19900</v>
       </c>
       <c r="I12" s="3">
-        <v>46400</v>
+        <v>46000</v>
       </c>
       <c r="J12" s="3">
-        <v>52500</v>
+        <v>52000</v>
       </c>
       <c r="K12" s="3">
         <v>25800</v>
@@ -913,25 +913,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>13300</v>
+        <v>13200</v>
       </c>
       <c r="E14" s="3">
-        <v>44600</v>
+        <v>44100</v>
       </c>
       <c r="F14" s="3">
-        <v>31600</v>
+        <v>31300</v>
       </c>
       <c r="G14" s="3">
-        <v>49700</v>
+        <v>49200</v>
       </c>
       <c r="H14" s="3">
-        <v>-119500</v>
+        <v>-118300</v>
       </c>
       <c r="I14" s="3">
-        <v>616600</v>
+        <v>610400</v>
       </c>
       <c r="J14" s="3">
-        <v>69900</v>
+        <v>69200</v>
       </c>
       <c r="K14" s="3">
         <v>6200</v>
@@ -998,25 +998,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>1134100</v>
+        <v>1122800</v>
       </c>
       <c r="E17" s="3">
-        <v>1139300</v>
+        <v>1128000</v>
       </c>
       <c r="F17" s="3">
-        <v>998900</v>
+        <v>989000</v>
       </c>
       <c r="G17" s="3">
-        <v>1051300</v>
+        <v>1040800</v>
       </c>
       <c r="H17" s="3">
-        <v>651200</v>
+        <v>644700</v>
       </c>
       <c r="I17" s="3">
-        <v>1284100</v>
+        <v>1271300</v>
       </c>
       <c r="J17" s="3">
-        <v>590000</v>
+        <v>584100</v>
       </c>
       <c r="K17" s="3">
         <v>503000</v>
@@ -1034,25 +1034,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>249800</v>
+        <v>247300</v>
       </c>
       <c r="E18" s="3">
-        <v>57200</v>
+        <v>56600</v>
       </c>
       <c r="F18" s="3">
-        <v>292200</v>
+        <v>289300</v>
       </c>
       <c r="G18" s="3">
-        <v>357500</v>
+        <v>353900</v>
       </c>
       <c r="H18" s="3">
-        <v>196600</v>
+        <v>194600</v>
       </c>
       <c r="I18" s="3">
-        <v>-654200</v>
+        <v>-647700</v>
       </c>
       <c r="J18" s="3">
-        <v>-52900</v>
+        <v>-52400</v>
       </c>
       <c r="K18" s="3">
         <v>92200</v>
@@ -1092,19 +1092,19 @@
         <v>4400</v>
       </c>
       <c r="F20" s="3">
-        <v>-63700</v>
+        <v>-63000</v>
       </c>
       <c r="G20" s="3">
-        <v>-63000</v>
+        <v>-62300</v>
       </c>
       <c r="H20" s="3">
-        <v>18600</v>
+        <v>18400</v>
       </c>
       <c r="I20" s="3">
-        <v>14600</v>
+        <v>14500</v>
       </c>
       <c r="J20" s="3">
-        <v>54000</v>
+        <v>53400</v>
       </c>
       <c r="K20" s="3">
         <v>-17700</v>
@@ -1122,25 +1122,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>616200</v>
+        <v>609000</v>
       </c>
       <c r="E21" s="3">
-        <v>395000</v>
+        <v>390100</v>
       </c>
       <c r="F21" s="3">
-        <v>507600</v>
+        <v>501700</v>
       </c>
       <c r="G21" s="3">
-        <v>597500</v>
+        <v>590700</v>
       </c>
       <c r="H21" s="3">
-        <v>428900</v>
+        <v>424000</v>
       </c>
       <c r="I21" s="3">
-        <v>-494200</v>
+        <v>-489700</v>
       </c>
       <c r="J21" s="3">
-        <v>100300</v>
+        <v>99000</v>
       </c>
       <c r="K21" s="3">
         <v>176900</v>
@@ -1158,19 +1158,19 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>28400</v>
+        <v>28100</v>
       </c>
       <c r="E22" s="3">
-        <v>45300</v>
+        <v>44900</v>
       </c>
       <c r="F22" s="3">
-        <v>21200</v>
+        <v>21000</v>
       </c>
       <c r="G22" s="3">
-        <v>11400</v>
+        <v>11300</v>
       </c>
       <c r="H22" s="3">
-        <v>59600</v>
+        <v>59000</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>17</v>
@@ -1194,22 +1194,22 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>224200</v>
+        <v>221900</v>
       </c>
       <c r="E23" s="3">
-        <v>16300</v>
+        <v>16100</v>
       </c>
       <c r="F23" s="3">
-        <v>207300</v>
+        <v>205200</v>
       </c>
       <c r="G23" s="3">
-        <v>283100</v>
+        <v>280300</v>
       </c>
       <c r="H23" s="3">
-        <v>155700</v>
+        <v>154100</v>
       </c>
       <c r="I23" s="3">
-        <v>-639600</v>
+        <v>-633200</v>
       </c>
       <c r="J23" s="3">
         <v>1100</v>
@@ -1230,25 +1230,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>79000</v>
+        <v>78200</v>
       </c>
       <c r="E24" s="3">
-        <v>84000</v>
+        <v>83200</v>
       </c>
       <c r="F24" s="3">
-        <v>192100</v>
+        <v>190100</v>
       </c>
       <c r="G24" s="3">
-        <v>113000</v>
+        <v>111900</v>
       </c>
       <c r="H24" s="3">
-        <v>54600</v>
+        <v>54000</v>
       </c>
       <c r="I24" s="3">
-        <v>-118700</v>
+        <v>-117500</v>
       </c>
       <c r="J24" s="3">
-        <v>26600</v>
+        <v>26300</v>
       </c>
       <c r="K24" s="3">
         <v>77300</v>
@@ -1302,25 +1302,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>145200</v>
+        <v>143700</v>
       </c>
       <c r="E26" s="3">
-        <v>-67700</v>
+        <v>-67100</v>
       </c>
       <c r="F26" s="3">
-        <v>15200</v>
+        <v>15100</v>
       </c>
       <c r="G26" s="3">
-        <v>170100</v>
+        <v>168400</v>
       </c>
       <c r="H26" s="3">
-        <v>101100</v>
+        <v>100100</v>
       </c>
       <c r="I26" s="3">
-        <v>-520900</v>
+        <v>-515700</v>
       </c>
       <c r="J26" s="3">
-        <v>-25500</v>
+        <v>-25300</v>
       </c>
       <c r="K26" s="3">
         <v>-10300</v>
@@ -1338,25 +1338,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>145700</v>
+        <v>144200</v>
       </c>
       <c r="E27" s="3">
-        <v>-67500</v>
+        <v>-66800</v>
       </c>
       <c r="F27" s="3">
-        <v>14800</v>
+        <v>14600</v>
       </c>
       <c r="G27" s="3">
-        <v>180000</v>
+        <v>178200</v>
       </c>
       <c r="H27" s="3">
-        <v>110600</v>
+        <v>109500</v>
       </c>
       <c r="I27" s="3">
-        <v>-496600</v>
+        <v>-491600</v>
       </c>
       <c r="J27" s="3">
-        <v>-9800</v>
+        <v>-9700</v>
       </c>
       <c r="K27" s="3">
         <v>-6600</v>
@@ -1413,13 +1413,13 @@
         <v>-2100</v>
       </c>
       <c r="E29" s="3">
-        <v>-418000</v>
+        <v>-413900</v>
       </c>
       <c r="F29" s="3">
-        <v>-201400</v>
+        <v>-199400</v>
       </c>
       <c r="G29" s="3">
-        <v>-8700</v>
+        <v>-8600</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>17</v>
@@ -1524,19 +1524,19 @@
         <v>-4400</v>
       </c>
       <c r="F32" s="3">
-        <v>63700</v>
+        <v>63000</v>
       </c>
       <c r="G32" s="3">
-        <v>63000</v>
+        <v>62300</v>
       </c>
       <c r="H32" s="3">
-        <v>-18600</v>
+        <v>-18400</v>
       </c>
       <c r="I32" s="3">
-        <v>-14600</v>
+        <v>-14500</v>
       </c>
       <c r="J32" s="3">
-        <v>-54000</v>
+        <v>-53400</v>
       </c>
       <c r="K32" s="3">
         <v>17700</v>
@@ -1554,25 +1554,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>143600</v>
+        <v>142100</v>
       </c>
       <c r="E33" s="3">
-        <v>-485500</v>
+        <v>-480700</v>
       </c>
       <c r="F33" s="3">
-        <v>-186600</v>
+        <v>-184800</v>
       </c>
       <c r="G33" s="3">
-        <v>171200</v>
+        <v>169500</v>
       </c>
       <c r="H33" s="3">
-        <v>110600</v>
+        <v>109500</v>
       </c>
       <c r="I33" s="3">
-        <v>-496600</v>
+        <v>-491600</v>
       </c>
       <c r="J33" s="3">
-        <v>-13600</v>
+        <v>-13500</v>
       </c>
       <c r="K33" s="3">
         <v>-473400</v>
@@ -1626,25 +1626,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>143600</v>
+        <v>142100</v>
       </c>
       <c r="E35" s="3">
-        <v>-485500</v>
+        <v>-480700</v>
       </c>
       <c r="F35" s="3">
-        <v>-186600</v>
+        <v>-184800</v>
       </c>
       <c r="G35" s="3">
-        <v>171200</v>
+        <v>169500</v>
       </c>
       <c r="H35" s="3">
-        <v>110600</v>
+        <v>109500</v>
       </c>
       <c r="I35" s="3">
-        <v>-496600</v>
+        <v>-491600</v>
       </c>
       <c r="J35" s="3">
-        <v>-13600</v>
+        <v>-13500</v>
       </c>
       <c r="K35" s="3">
         <v>-473400</v>
@@ -1735,25 +1735,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>741600</v>
+        <v>734200</v>
       </c>
       <c r="E41" s="3">
-        <v>383900</v>
+        <v>380000</v>
       </c>
       <c r="F41" s="3">
-        <v>660500</v>
+        <v>653900</v>
       </c>
       <c r="G41" s="3">
-        <v>1240400</v>
+        <v>1228000</v>
       </c>
       <c r="H41" s="3">
-        <v>243900</v>
+        <v>241500</v>
       </c>
       <c r="I41" s="3">
-        <v>392900</v>
+        <v>389000</v>
       </c>
       <c r="J41" s="3">
-        <v>658000</v>
+        <v>651400</v>
       </c>
       <c r="K41" s="3">
         <v>1214800</v>
@@ -1774,22 +1774,22 @@
         <v>5400</v>
       </c>
       <c r="E42" s="3">
-        <v>48200</v>
+        <v>47700</v>
       </c>
       <c r="F42" s="3">
         <v>200</v>
       </c>
       <c r="G42" s="3">
-        <v>81300</v>
+        <v>80500</v>
       </c>
       <c r="H42" s="3">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="I42" s="3">
-        <v>12600</v>
+        <v>12500</v>
       </c>
       <c r="J42" s="3">
-        <v>14400</v>
+        <v>14300</v>
       </c>
       <c r="K42" s="3">
         <v>46200</v>
@@ -1807,25 +1807,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>137200</v>
+        <v>135800</v>
       </c>
       <c r="E43" s="3">
-        <v>92000</v>
+        <v>91100</v>
       </c>
       <c r="F43" s="3">
-        <v>69600</v>
+        <v>68900</v>
       </c>
       <c r="G43" s="3">
-        <v>77900</v>
+        <v>77100</v>
       </c>
       <c r="H43" s="3">
-        <v>87100</v>
+        <v>86300</v>
       </c>
       <c r="I43" s="3">
-        <v>89500</v>
+        <v>88600</v>
       </c>
       <c r="J43" s="3">
-        <v>81800</v>
+        <v>81000</v>
       </c>
       <c r="K43" s="3">
         <v>57000</v>
@@ -1843,25 +1843,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>323700</v>
+        <v>320500</v>
       </c>
       <c r="E44" s="3">
-        <v>272900</v>
+        <v>270200</v>
       </c>
       <c r="F44" s="3">
-        <v>244500</v>
+        <v>242000</v>
       </c>
       <c r="G44" s="3">
-        <v>225200</v>
+        <v>223000</v>
       </c>
       <c r="H44" s="3">
-        <v>224000</v>
+        <v>221800</v>
       </c>
       <c r="I44" s="3">
-        <v>189200</v>
+        <v>187300</v>
       </c>
       <c r="J44" s="3">
-        <v>231700</v>
+        <v>229400</v>
       </c>
       <c r="K44" s="3">
         <v>166200</v>
@@ -1879,25 +1879,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>68800</v>
+        <v>68100</v>
       </c>
       <c r="E45" s="3">
-        <v>70900</v>
+        <v>70200</v>
       </c>
       <c r="F45" s="3">
-        <v>24500</v>
+        <v>24200</v>
       </c>
       <c r="G45" s="3">
-        <v>30200</v>
+        <v>29900</v>
       </c>
       <c r="H45" s="3">
-        <v>33300</v>
+        <v>33000</v>
       </c>
       <c r="I45" s="3">
-        <v>22000</v>
+        <v>21800</v>
       </c>
       <c r="J45" s="3">
-        <v>26200</v>
+        <v>25900</v>
       </c>
       <c r="K45" s="3">
         <v>18100</v>
@@ -1915,25 +1915,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1276700</v>
+        <v>1264000</v>
       </c>
       <c r="E46" s="3">
-        <v>867900</v>
+        <v>859200</v>
       </c>
       <c r="F46" s="3">
-        <v>999300</v>
+        <v>989300</v>
       </c>
       <c r="G46" s="3">
-        <v>1034800</v>
+        <v>1024400</v>
       </c>
       <c r="H46" s="3">
-        <v>598100</v>
+        <v>592100</v>
       </c>
       <c r="I46" s="3">
-        <v>706300</v>
+        <v>699200</v>
       </c>
       <c r="J46" s="3">
-        <v>1012000</v>
+        <v>1001900</v>
       </c>
       <c r="K46" s="3">
         <v>1502300</v>
@@ -1951,25 +1951,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>247600</v>
+        <v>245200</v>
       </c>
       <c r="E47" s="3">
-        <v>160600</v>
+        <v>159000</v>
       </c>
       <c r="F47" s="3">
-        <v>135400</v>
+        <v>134000</v>
       </c>
       <c r="G47" s="3">
-        <v>44100</v>
+        <v>43700</v>
       </c>
       <c r="H47" s="3">
-        <v>18900</v>
+        <v>18700</v>
       </c>
       <c r="I47" s="3">
         <v>9100</v>
       </c>
       <c r="J47" s="3">
-        <v>7400</v>
+        <v>7300</v>
       </c>
       <c r="K47" s="3">
         <v>63900</v>
@@ -1987,25 +1987,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5153400</v>
+        <v>5101900</v>
       </c>
       <c r="E48" s="3">
-        <v>4934800</v>
+        <v>4885500</v>
       </c>
       <c r="F48" s="3">
-        <v>5493200</v>
+        <v>5438400</v>
       </c>
       <c r="G48" s="3">
-        <v>5546700</v>
+        <v>5491300</v>
       </c>
       <c r="H48" s="3">
-        <v>5609800</v>
+        <v>5553800</v>
       </c>
       <c r="I48" s="3">
-        <v>5473000</v>
+        <v>5418300</v>
       </c>
       <c r="J48" s="3">
-        <v>5800800</v>
+        <v>5742900</v>
       </c>
       <c r="K48" s="3">
         <v>5014800</v>
@@ -2023,25 +2023,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>127100</v>
+        <v>125800</v>
       </c>
       <c r="E49" s="3">
-        <v>127100</v>
+        <v>125800</v>
       </c>
       <c r="F49" s="3">
-        <v>127100</v>
+        <v>125800</v>
       </c>
       <c r="G49" s="3">
-        <v>127100</v>
+        <v>125800</v>
       </c>
       <c r="H49" s="3">
-        <v>127100</v>
+        <v>125800</v>
       </c>
       <c r="I49" s="3">
-        <v>127100</v>
+        <v>125800</v>
       </c>
       <c r="J49" s="3">
-        <v>127100</v>
+        <v>125800</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -2131,25 +2131,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>39300</v>
+        <v>38900</v>
       </c>
       <c r="E52" s="3">
-        <v>26900</v>
+        <v>26600</v>
       </c>
       <c r="F52" s="3">
-        <v>11000</v>
+        <v>10900</v>
       </c>
       <c r="G52" s="3">
-        <v>67300</v>
+        <v>66700</v>
       </c>
       <c r="H52" s="3">
-        <v>25400</v>
+        <v>25200</v>
       </c>
       <c r="I52" s="3">
-        <v>36400</v>
+        <v>36000</v>
       </c>
       <c r="J52" s="3">
-        <v>37600</v>
+        <v>37300</v>
       </c>
       <c r="K52" s="3">
         <v>18500</v>
@@ -2203,25 +2203,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6844000</v>
+        <v>6775700</v>
       </c>
       <c r="E54" s="3">
-        <v>6117200</v>
+        <v>6056100</v>
       </c>
       <c r="F54" s="3">
-        <v>6766000</v>
+        <v>6698400</v>
       </c>
       <c r="G54" s="3">
-        <v>6765700</v>
+        <v>6698100</v>
       </c>
       <c r="H54" s="3">
-        <v>6379200</v>
+        <v>6315600</v>
       </c>
       <c r="I54" s="3">
-        <v>6351800</v>
+        <v>6288400</v>
       </c>
       <c r="J54" s="3">
-        <v>6984900</v>
+        <v>6915200</v>
       </c>
       <c r="K54" s="3">
         <v>6599500</v>
@@ -2271,25 +2271,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>128100</v>
+        <v>126800</v>
       </c>
       <c r="E57" s="3">
-        <v>102800</v>
+        <v>101800</v>
       </c>
       <c r="F57" s="3">
-        <v>97400</v>
+        <v>96500</v>
       </c>
       <c r="G57" s="3">
-        <v>335400</v>
+        <v>332100</v>
       </c>
       <c r="H57" s="3">
-        <v>92100</v>
+        <v>91200</v>
       </c>
       <c r="I57" s="3">
-        <v>53500</v>
+        <v>52900</v>
       </c>
       <c r="J57" s="3">
-        <v>82400</v>
+        <v>81600</v>
       </c>
       <c r="K57" s="3">
         <v>60100</v>
@@ -2307,19 +2307,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6900</v>
+        <v>6800</v>
       </c>
       <c r="E58" s="3">
-        <v>6600</v>
+        <v>6500</v>
       </c>
       <c r="F58" s="3">
-        <v>9900</v>
+        <v>9800</v>
       </c>
       <c r="G58" s="3">
-        <v>107000</v>
+        <v>105900</v>
       </c>
       <c r="H58" s="3">
-        <v>105100</v>
+        <v>104000</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>17</v>
@@ -2343,25 +2343,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>241300</v>
+        <v>238900</v>
       </c>
       <c r="E59" s="3">
-        <v>180100</v>
+        <v>178300</v>
       </c>
       <c r="F59" s="3">
-        <v>176200</v>
+        <v>174400</v>
       </c>
       <c r="G59" s="3">
-        <v>163300</v>
+        <v>161700</v>
       </c>
       <c r="H59" s="3">
-        <v>107100</v>
+        <v>106000</v>
       </c>
       <c r="I59" s="3">
-        <v>141000</v>
+        <v>139600</v>
       </c>
       <c r="J59" s="3">
-        <v>74200</v>
+        <v>73400</v>
       </c>
       <c r="K59" s="3">
         <v>64600</v>
@@ -2379,25 +2379,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>376300</v>
+        <v>372500</v>
       </c>
       <c r="E60" s="3">
-        <v>289500</v>
+        <v>286600</v>
       </c>
       <c r="F60" s="3">
-        <v>283600</v>
+        <v>280700</v>
       </c>
       <c r="G60" s="3">
-        <v>359600</v>
+        <v>356000</v>
       </c>
       <c r="H60" s="3">
-        <v>304200</v>
+        <v>301200</v>
       </c>
       <c r="I60" s="3">
-        <v>194400</v>
+        <v>192500</v>
       </c>
       <c r="J60" s="3">
-        <v>156600</v>
+        <v>155100</v>
       </c>
       <c r="K60" s="3">
         <v>124800</v>
@@ -2415,25 +2415,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>889400</v>
+        <v>880500</v>
       </c>
       <c r="E61" s="3">
-        <v>695100</v>
+        <v>688200</v>
       </c>
       <c r="F61" s="3">
-        <v>692500</v>
+        <v>685600</v>
       </c>
       <c r="G61" s="3">
-        <v>616300</v>
+        <v>610100</v>
       </c>
       <c r="H61" s="3">
-        <v>587600</v>
+        <v>581700</v>
       </c>
       <c r="I61" s="3">
-        <v>826800</v>
+        <v>818500</v>
       </c>
       <c r="J61" s="3">
-        <v>814800</v>
+        <v>806700</v>
       </c>
       <c r="K61" s="3">
         <v>813700</v>
@@ -2451,25 +2451,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>759200</v>
+        <v>751700</v>
       </c>
       <c r="E62" s="3">
-        <v>740300</v>
+        <v>733000</v>
       </c>
       <c r="F62" s="3">
-        <v>795200</v>
+        <v>787300</v>
       </c>
       <c r="G62" s="3">
-        <v>730500</v>
+        <v>723200</v>
       </c>
       <c r="H62" s="3">
-        <v>720600</v>
+        <v>713500</v>
       </c>
       <c r="I62" s="3">
-        <v>737700</v>
+        <v>730400</v>
       </c>
       <c r="J62" s="3">
-        <v>904200</v>
+        <v>895100</v>
       </c>
       <c r="K62" s="3">
         <v>748500</v>
@@ -2595,25 +2595,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2016400</v>
+        <v>1996300</v>
       </c>
       <c r="E66" s="3">
-        <v>1720500</v>
+        <v>1703400</v>
       </c>
       <c r="F66" s="3">
-        <v>1866700</v>
+        <v>1848100</v>
       </c>
       <c r="G66" s="3">
-        <v>1762400</v>
+        <v>1744800</v>
       </c>
       <c r="H66" s="3">
-        <v>1693900</v>
+        <v>1676900</v>
       </c>
       <c r="I66" s="3">
-        <v>1846000</v>
+        <v>1827500</v>
       </c>
       <c r="J66" s="3">
-        <v>1985300</v>
+        <v>1965500</v>
       </c>
       <c r="K66" s="3">
         <v>1809100</v>
@@ -2791,25 +2791,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-3414600</v>
+        <v>-3380500</v>
       </c>
       <c r="E72" s="3">
-        <v>-3558200</v>
+        <v>-3522700</v>
       </c>
       <c r="F72" s="3">
-        <v>-3072700</v>
+        <v>-3042000</v>
       </c>
       <c r="G72" s="3">
-        <v>-2886000</v>
+        <v>-2857200</v>
       </c>
       <c r="H72" s="3">
-        <v>-3059800</v>
+        <v>-3029300</v>
       </c>
       <c r="I72" s="3">
-        <v>-3170400</v>
+        <v>-3138800</v>
       </c>
       <c r="J72" s="3">
-        <v>-2673800</v>
+        <v>-2647100</v>
       </c>
       <c r="K72" s="3">
         <v>-2652000</v>
@@ -2935,25 +2935,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4827600</v>
+        <v>4779400</v>
       </c>
       <c r="E76" s="3">
-        <v>4396600</v>
+        <v>4352700</v>
       </c>
       <c r="F76" s="3">
-        <v>4899300</v>
+        <v>4850300</v>
       </c>
       <c r="G76" s="3">
-        <v>5003300</v>
+        <v>4953300</v>
       </c>
       <c r="H76" s="3">
-        <v>4685400</v>
+        <v>4638600</v>
       </c>
       <c r="I76" s="3">
-        <v>4505900</v>
+        <v>4460900</v>
       </c>
       <c r="J76" s="3">
-        <v>4999700</v>
+        <v>4949800</v>
       </c>
       <c r="K76" s="3">
         <v>4790400</v>
@@ -3048,25 +3048,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>143600</v>
+        <v>142100</v>
       </c>
       <c r="E81" s="3">
-        <v>-485500</v>
+        <v>-480700</v>
       </c>
       <c r="F81" s="3">
-        <v>-186600</v>
+        <v>-184800</v>
       </c>
       <c r="G81" s="3">
-        <v>171200</v>
+        <v>169500</v>
       </c>
       <c r="H81" s="3">
-        <v>110600</v>
+        <v>109500</v>
       </c>
       <c r="I81" s="3">
-        <v>-496600</v>
+        <v>-491600</v>
       </c>
       <c r="J81" s="3">
-        <v>-13600</v>
+        <v>-13500</v>
       </c>
       <c r="K81" s="3">
         <v>-473400</v>
@@ -3100,25 +3100,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>362700</v>
+        <v>359100</v>
       </c>
       <c r="E83" s="3">
-        <v>332600</v>
+        <v>329300</v>
       </c>
       <c r="F83" s="3">
-        <v>278400</v>
+        <v>275600</v>
       </c>
       <c r="G83" s="3">
-        <v>302200</v>
+        <v>299200</v>
       </c>
       <c r="H83" s="3">
-        <v>213100</v>
+        <v>211000</v>
       </c>
       <c r="I83" s="3">
-        <v>145100</v>
+        <v>143600</v>
       </c>
       <c r="J83" s="3">
-        <v>99000</v>
+        <v>98000</v>
       </c>
       <c r="K83" s="3">
         <v>103000</v>
@@ -3316,25 +3316,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>524900</v>
+        <v>519700</v>
       </c>
       <c r="E89" s="3">
-        <v>289000</v>
+        <v>286200</v>
       </c>
       <c r="F89" s="3">
-        <v>497200</v>
+        <v>492300</v>
       </c>
       <c r="G89" s="3">
-        <v>644900</v>
+        <v>638500</v>
       </c>
       <c r="H89" s="3">
-        <v>227500</v>
+        <v>225200</v>
       </c>
       <c r="I89" s="3">
-        <v>92700</v>
+        <v>91800</v>
       </c>
       <c r="J89" s="3">
-        <v>38400</v>
+        <v>38000</v>
       </c>
       <c r="K89" s="3">
         <v>156300</v>
@@ -3368,25 +3368,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-551400</v>
+        <v>-545900</v>
       </c>
       <c r="E91" s="3">
-        <v>-397700</v>
+        <v>-393800</v>
       </c>
       <c r="F91" s="3">
-        <v>-387100</v>
+        <v>-383200</v>
       </c>
       <c r="G91" s="3">
-        <v>-259200</v>
+        <v>-256600</v>
       </c>
       <c r="H91" s="3">
-        <v>-294300</v>
+        <v>-291400</v>
       </c>
       <c r="I91" s="3">
-        <v>-317900</v>
+        <v>-314700</v>
       </c>
       <c r="J91" s="3">
-        <v>-474600</v>
+        <v>-469900</v>
       </c>
       <c r="K91" s="3">
         <v>-409400</v>
@@ -3476,25 +3476,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-543000</v>
+        <v>-537500</v>
       </c>
       <c r="E94" s="3">
-        <v>-508900</v>
+        <v>-503900</v>
       </c>
       <c r="F94" s="3">
-        <v>-364800</v>
+        <v>-361200</v>
       </c>
       <c r="G94" s="3">
-        <v>-335100</v>
+        <v>-331800</v>
       </c>
       <c r="H94" s="3">
-        <v>-259200</v>
+        <v>-256600</v>
       </c>
       <c r="I94" s="3">
-        <v>-353200</v>
+        <v>-349700</v>
       </c>
       <c r="J94" s="3">
-        <v>-571300</v>
+        <v>-565600</v>
       </c>
       <c r="K94" s="3">
         <v>662100</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>-14600</v>
+        <v>-14400</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3672,25 +3672,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>375800</v>
+        <v>372100</v>
       </c>
       <c r="E100" s="3">
-        <v>-56700</v>
+        <v>-56200</v>
       </c>
       <c r="F100" s="3">
-        <v>-92100</v>
+        <v>-91200</v>
       </c>
       <c r="G100" s="3">
-        <v>66500</v>
+        <v>65800</v>
       </c>
       <c r="H100" s="3">
-        <v>-117300</v>
+        <v>-116100</v>
       </c>
       <c r="I100" s="3">
-        <v>-4600</v>
+        <v>-4500</v>
       </c>
       <c r="J100" s="3">
-        <v>-21000</v>
+        <v>-20800</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -3744,25 +3744,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>356700</v>
+        <v>354200</v>
       </c>
       <c r="E102" s="3">
-        <v>-276600</v>
+        <v>-273900</v>
       </c>
       <c r="F102" s="3">
-        <v>40300</v>
+        <v>39900</v>
       </c>
       <c r="G102" s="3">
-        <v>376300</v>
+        <v>372500</v>
       </c>
       <c r="H102" s="3">
-        <v>-149000</v>
+        <v>-147500</v>
       </c>
       <c r="I102" s="3">
-        <v>-265100</v>
+        <v>-262400</v>
       </c>
       <c r="J102" s="3">
-        <v>-553900</v>
+        <v>-548400</v>
       </c>
       <c r="K102" s="3">
         <v>818400</v>
